--- a/artfynd/A 15852-2022 artfynd.xlsx
+++ b/artfynd/A 15852-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15852-2022 artfynd.xlsx
+++ b/artfynd/A 15852-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79140222</v>
+        <v>79140200</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542947.4070618761</v>
+        <v>542865</v>
       </c>
       <c r="R2" t="n">
-        <v>7183261.837097529</v>
+        <v>7183293</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79140221</v>
+        <v>79140223</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542947.4070618761</v>
+        <v>542957</v>
       </c>
       <c r="R3" t="n">
-        <v>7183261.837097529</v>
+        <v>7183256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,21 +845,11 @@
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +861,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79140223</v>
+        <v>79140221</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542957.3178943968</v>
+        <v>542947</v>
       </c>
       <c r="R4" t="n">
-        <v>7183256.003701837</v>
+        <v>7183262</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,21 +947,11 @@
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,7 +963,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79140200</v>
+        <v>79140199</v>
       </c>
       <c r="B5" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542864.9289118379</v>
+        <v>542851</v>
       </c>
       <c r="R5" t="n">
-        <v>7183292.669440813</v>
+        <v>7183292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,21 +1049,11 @@
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,7 +1065,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79140201</v>
+        <v>79140222</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542891.0183209396</v>
+        <v>542947</v>
       </c>
       <c r="R6" t="n">
-        <v>7183290.907043196</v>
+        <v>7183262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,21 +1151,11 @@
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1167,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1260,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79140199</v>
+        <v>79140220</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542850.8314032515</v>
+        <v>542914</v>
       </c>
       <c r="R7" t="n">
-        <v>7183292.468842333</v>
+        <v>7183276</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,21 +1253,11 @@
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1356,11 +1266,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1374,118 +1279,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>79140220</v>
-      </c>
-      <c r="B8" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Näsberget, SV Granliden, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>542914.29975877</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7183276.301974291</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2019-07-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2019-07-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Andreas Garpebring, Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
